--- a/docs/unit-economics.xlsx
+++ b/docs/unit-economics.xlsx
@@ -114,24 +114,12 @@
   </cellStyleXfs>
   <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -555,119 +543,119 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>SharePix unit economics</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Rebuilt September 2026 for the current lineup: one free event per account, one paid plan at $79.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>This is a rebuild, not an edit</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>The previous model was not available to work from. Everything here was derived fresh from the</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>codebase and from published cloud pricing. Treat any figure you recognise from the old model as a</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>coincidence rather than a carried-forward value.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>Why the old model could not be patched</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>It predates three changes that each move the answer:</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   1.  Photos are now UNLIMITED on the paid plan. The old model multiplied a fixed cap by a cost</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">       per photo. There is no cap to multiply, so cost per event is now a distribution, not a number.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">       That is why this workbook leads with a break-even grid instead of a single margin figure.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   2.  A free tier exists. Its cost is real and is carried by paid events, so the number that matters</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">       is blended margin per PAID event, not gross margin per event.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   3.  Retention is 60-day window + 12-month gallery + 90-day archive. Storage is held ~17 months,</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">       not for the length of the event. This is the single largest cost driver and the old model</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">       used a much shorter horizon.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>Colour legend</t>
         </is>
@@ -681,7 +669,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   Black     a formula. Do not overwrite these.</t>
         </is>
@@ -695,91 +683,91 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>How much of this is real</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Marked per row on Assumptions in the Confidence column.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   CODE      taken from this repository. Reliable. Changing it in the sheet does not change the</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">             product, and a test now fails if the two disagree.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   PUBLISHED cloud list pricing, correct at the time of writing but not fetched live. Re-check</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">             before making a decision that turns on the exact figure.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">   ESTIMATE  a guess. These are the rows to replace with measured values first, and the ones</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">             most likely to be wrong. They are shaded yellow.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="31" t="inlineStr">
         <is>
           <t>The finding worth reading before anything else</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Every object is stored TWICE. Objects are written to S3, mirrored to Cloudflare R2, and R2 serves</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>all reads — but the S3 copy is never removed early. It sits until an 800-day lifecycle backstop</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>expires it, roughly 280 days after the event has been deleted everywhere a customer can see.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>See "Dual storage" on the Unit economics sheet for what that costs and what could be done.</t>
         </is>
@@ -796,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -820,6 +808,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -1208,11 +1197,11 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>S3 lifecycle backstop</t>
+          <t>S3 copy retention</t>
         </is>
       </c>
       <c r="B21" s="14" t="n">
-        <v>800</v>
+        <v>90</v>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
@@ -1226,7 +1215,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>expire-event-media-backstop in amplify/backend.ts</t>
+          <t>S3_COPY_RETENTION_DAYS in amplify/backend.ts. Was 800; shortened once prints moved to R2</t>
         </is>
       </c>
     </row>
@@ -1799,6 +1788,19 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2427,7 +2429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2467,6 +2469,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
@@ -2790,6 +2793,7 @@
         <v/>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="25" t="inlineStr">
         <is>
@@ -2801,6 +2805,7 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="31" t="inlineStr">
         <is>
@@ -2819,7 +2824,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>photoReviewThreshold in lib/fairUse.ts. Flags for a look; blocks nothing</t>
+          <t>photoReviewThreshold. Flags for a look; blocks nothing. Unchanged</t>
         </is>
       </c>
     </row>
@@ -2830,11 +2835,11 @@
         </is>
       </c>
       <c r="B22" s="14" t="n">
-        <v>50000</v>
+        <v>36800</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>photoAbuseThreshold. This one blocks uploads</t>
+          <t>photoAbuseThreshold, now derived from break-even in lib/fairUse.ts</t>
         </is>
       </c>
     </row>
@@ -2854,6 +2859,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="31" t="inlineStr">
         <is>
@@ -2940,6 +2946,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
   </sheetData>
   <conditionalFormatting sqref="B8:G16">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
